--- a/data/prices/current_prices.xlsx
+++ b/data/prices/current_prices.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="PO" sheetId="1" r:id="rId1"/>
-    <sheet name="价目表0506" sheetId="7" r:id="rId2"/>
+    <sheet name="价目表0601" sheetId="7" r:id="rId2"/>
     <sheet name="价目表名称" sheetId="4" r:id="rId3"/>
     <sheet name="历史" sheetId="5" state="hidden" r:id="rId4"/>
     <sheet name="一揽子" sheetId="6" state="hidden" r:id="rId5"/>
     <sheet name="型号" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PO!$A$1:$K$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">价目表0506!$A$1:$S$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PO!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">价目表0601!$A$1:$S$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">历史!$A$2:$R$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">一揽子!$A$2:$BD$20</definedName>
   </definedNames>
@@ -41,7 +41,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
-    <author>haixia.lu</author>
   </authors>
   <commentList>
     <comment ref="G1" authorId="0">
@@ -66,34 +65,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>haixia.lu:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-工程批</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="197">
   <si>
     <t>芯片型号</t>
   </si>
@@ -174,9 +151,6 @@
   </si>
   <si>
     <t>BM1370</t>
-  </si>
-  <si>
-    <t>更新</t>
   </si>
   <si>
     <t>BM2382</t>
@@ -906,7 +880,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -928,12 +902,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1263,7 +1231,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1287,16 +1255,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1305,89 +1273,89 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1405,10 +1373,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1439,47 +1408,52 @@
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1806,7 +1780,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="9.5" style="13" customWidth="1"/>
@@ -1814,55 +1788,57 @@
     <col min="3" max="3" width="16.25" style="12" customWidth="1"/>
     <col min="4" max="4" width="27.0416666666667" style="18" customWidth="1"/>
     <col min="5" max="6" width="8.83333333333333" style="13"/>
-    <col min="7" max="7" width="8.83333333333333" style="16"/>
-    <col min="8" max="8" width="10.4166666666667" style="16" customWidth="1"/>
-    <col min="9" max="9" width="12.775" style="13" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" style="13"/>
-    <col min="11" max="11" width="8.83333333333333" style="19"/>
-    <col min="12" max="16384" width="8.83333333333333" style="13"/>
+    <col min="7" max="7" width="8.83333333333333" style="19" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.4166666666667" style="19" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.775" style="13" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83333333333333" style="13" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" style="20" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="8.83333333333333" style="13" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="8.83333333333333" style="13" customWidth="1"/>
+    <col min="16" max="16384" width="8.83333333333333" style="13"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="1" ht="12" customHeight="1" spans="1:11">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="23" t="s">
+      <c r="G1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="25"/>
+      <c r="K1" s="26"/>
     </row>
     <row r="2" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <v>3.7699</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="31">
         <v>3.76988841896588</v>
       </c>
       <c r="I2" s="13">
@@ -1873,29 +1849,29 @@
         <f>A2=G2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="19">
+      <c r="K2" s="20">
         <f>D2-I2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="14" customFormat="1" ht="14" spans="1:11">
-      <c r="A3" s="31" t="s">
+    <row r="3" s="13" customFormat="1" ht="14" spans="1:11">
+      <c r="A3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <v>57.6365</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="13"/>
+      <c r="G3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="32">
         <v>57.6364608607962</v>
       </c>
       <c r="I3" s="13">
@@ -1903,31 +1879,31 @@
         <v>57.6365</v>
       </c>
       <c r="J3" s="13" t="b">
-        <f t="shared" ref="J3:J33" si="1">A3=G3</f>
+        <f t="shared" ref="J3:J31" si="1">A3=G3</f>
         <v>1</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="20">
         <f t="shared" ref="K3:K31" si="2">D3-I3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C4" s="27" t="s">
+      <c r="B4" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>2.4828</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>2.48283105927098</v>
       </c>
       <c r="I4" s="13">
@@ -1938,28 +1914,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>4.0901</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <v>4.09005945062342</v>
       </c>
       <c r="I5" s="13">
@@ -1970,28 +1946,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>5.0536</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="31">
         <v>5.05361190736309</v>
       </c>
       <c r="I6" s="13">
@@ -2002,28 +1978,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <v>3.5349</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>3.53491405257816</v>
       </c>
       <c r="I7" s="13">
@@ -2034,28 +2010,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>200.2487</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>200.24868246562</v>
       </c>
       <c r="I8" s="13">
@@ -2066,28 +2042,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="B9" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>5.2113</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <v>5.21131854227521</v>
       </c>
       <c r="I9" s="13">
@@ -2098,28 +2074,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="B10" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>3.7914</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <v>3.79144978923285</v>
       </c>
       <c r="I10" s="13">
@@ -2130,28 +2106,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="B11" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <v>3.4623</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <v>3.46228106759082</v>
       </c>
       <c r="I11" s="13">
@@ -2162,28 +2138,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>3.4712</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <v>3.47120606759082</v>
       </c>
       <c r="I12" s="13">
@@ -2194,28 +2170,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <v>3.4712</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>3.47120606759082</v>
       </c>
       <c r="I13" s="13">
@@ -2226,28 +2202,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C14" s="27" t="s">
+      <c r="B14" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C14" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <v>3.4712</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>3.47120606759082</v>
       </c>
       <c r="I14" s="13">
@@ -2258,28 +2234,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <v>3.4712</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>3.47120606759082</v>
       </c>
       <c r="I15" s="13">
@@ -2290,28 +2266,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>3.4712</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>3.47120606759082</v>
       </c>
       <c r="I16" s="13">
@@ -2322,28 +2298,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <v>250.5673</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <v>250.567303763432</v>
       </c>
       <c r="I17" s="13">
@@ -2354,28 +2330,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <v>55.1336</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="31">
         <v>55.1336469658512</v>
       </c>
       <c r="I18" s="13">
@@ -2386,28 +2362,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <v>2324.8445</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="31">
         <v>2324.84445310543</v>
       </c>
       <c r="I19" s="13">
@@ -2418,28 +2394,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C20" s="27" t="s">
+      <c r="B20" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <v>2.2925</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="31">
         <v>2.29252788136591</v>
       </c>
       <c r="I20" s="13">
@@ -2450,63 +2426,61 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="15" customFormat="1" ht="14" spans="1:11">
-      <c r="A21" s="36" t="s">
+    <row r="21" s="14" customFormat="1" ht="14" spans="1:11">
+      <c r="A21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="37">
-        <v>202605</v>
-      </c>
-      <c r="C21" s="37" t="s">
+      <c r="B21" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C21" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="35">
         <v>8.4438</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="39" t="s">
+      <c r="E21" s="14"/>
+      <c r="G21" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="37">
         <v>8.44382699824801</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <f t="shared" si="0"/>
         <v>8.4438</v>
       </c>
-      <c r="J21" s="15" t="b">
+      <c r="J21" s="13" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A22" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C22" s="27" t="s">
+    <row r="22" s="15" customFormat="1" ht="14" spans="1:11">
+      <c r="A22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C22" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="40">
         <v>2.9837</v>
       </c>
-      <c r="G22" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="30">
+      <c r="G22" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="42">
         <v>2.9837211539186</v>
       </c>
       <c r="I22" s="13">
@@ -2517,28 +2491,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" s="16" customFormat="1" ht="14" spans="1:11">
-      <c r="A23" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C23" s="43" t="s">
+      <c r="A23" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C23" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="45">
         <v>12.745</v>
       </c>
-      <c r="G23" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="30">
+      <c r="G23" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="42">
         <v>12.7449617527045</v>
       </c>
       <c r="I23" s="13">
@@ -2549,28 +2523,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" s="16" customFormat="1" ht="14" spans="1:11">
-      <c r="A24" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C24" s="43" t="s">
+      <c r="A24" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C24" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="45">
         <v>31.8244</v>
       </c>
-      <c r="G24" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="30">
+      <c r="G24" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="42">
         <v>31.8244289707207</v>
       </c>
       <c r="I24" s="13">
@@ -2581,28 +2555,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" s="16" customFormat="1" ht="14" spans="1:11">
-      <c r="A25" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C25" s="43" t="s">
+      <c r="A25" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C25" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="45">
         <v>11.2214</v>
       </c>
-      <c r="G25" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="30">
+      <c r="G25" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="42">
         <v>11.2213508213799</v>
       </c>
       <c r="I25" s="13">
@@ -2613,29 +2587,29 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" s="17" customFormat="1" ht="14" spans="1:11">
-      <c r="A26" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C26" s="47" t="s">
+    <row r="26" s="16" customFormat="1" ht="14" spans="1:11">
+      <c r="A26" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C26" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="45">
         <v>1490.092</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="G26" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="35">
+      <c r="E26" s="15"/>
+      <c r="G26" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="42">
         <v>1490.09197028286</v>
       </c>
       <c r="I26" s="13">
@@ -2646,28 +2620,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" s="16" customFormat="1" ht="14" spans="1:11">
-      <c r="A27" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C27" s="43" t="s">
+      <c r="A27" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C27" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="45">
         <v>17.4733</v>
       </c>
-      <c r="G27" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="30">
+      <c r="G27" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="42">
         <v>17.4732997056972</v>
       </c>
       <c r="I27" s="13">
@@ -2678,28 +2652,28 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A28" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C28" s="43" t="s">
+    <row r="28" s="15" customFormat="1" ht="14" spans="1:11">
+      <c r="A28" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C28" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="40">
         <v>7.8846</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="30">
+      <c r="G28" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="37">
         <v>7.88456817764754</v>
       </c>
       <c r="I28" s="13">
@@ -2707,64 +2681,64 @@
         <v>7.8846</v>
       </c>
       <c r="J28" s="13" t="b">
-        <f>A28=G28</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="14" customFormat="1" ht="14" spans="1:11">
-      <c r="A29" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C29" s="47" t="s">
+    <row r="29" s="17" customFormat="1" ht="17" spans="1:11">
+      <c r="A29" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C29" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="33">
-        <v>31.5304</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="G29" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" s="30">
-        <v>31.5303552800784</v>
+      <c r="D29" s="50">
+        <v>28.4759</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="G29" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="37">
+        <v>28.4758804623615</v>
       </c>
       <c r="I29" s="13">
         <f>ROUND(H29,4)</f>
-        <v>31.5304</v>
+        <v>28.4759</v>
       </c>
       <c r="J29" s="13" t="b">
-        <f>A29=G29</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" s="13" customFormat="1" ht="14" spans="1:11">
-      <c r="A30" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="27">
-        <v>202605</v>
-      </c>
-      <c r="C30" s="43" t="s">
+    <row r="30" s="15" customFormat="1" spans="1:11">
+      <c r="A30" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C30" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="40">
         <v>21.1352</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="30">
+      <c r="G30" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="16">
         <v>21.1352354235823</v>
       </c>
       <c r="I30" s="13">
@@ -2772,51 +2746,124 @@
         <v>21.1352</v>
       </c>
       <c r="J30" s="13" t="b">
-        <f>A30=G30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="1" ht="17" spans="1:11">
-      <c r="A31" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="37">
-        <v>202605</v>
-      </c>
-      <c r="C31" s="50" t="s">
+    <row r="31" s="14" customFormat="1" spans="1:11">
+      <c r="A31" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="28">
+        <v>202606</v>
+      </c>
+      <c r="C31" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="35">
         <v>37.6147</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="H31" s="40">
+      <c r="E31" s="14"/>
+      <c r="G31" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="16">
         <v>37.6146582153707</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="13">
         <f>ROUND(H31,4)</f>
         <v>37.6147</v>
       </c>
-      <c r="J31" s="15" t="b">
-        <f>A31=G31</f>
+      <c r="J31" s="13" t="b">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K31" s="41">
+      <c r="K31" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
+    <row r="32" s="15" customFormat="1" spans="1:11">
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="20"/>
+    </row>
+    <row r="33" s="15" customFormat="1" spans="2:11">
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="20"/>
+    </row>
+    <row r="34" s="13" customFormat="1" spans="2:11">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="20"/>
+    </row>
+    <row r="35" s="13" customFormat="1" spans="2:11">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="20"/>
+    </row>
+    <row r="36" s="13" customFormat="1" spans="2:11">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="20"/>
+    </row>
+    <row r="37" s="13" customFormat="1" spans="2:11">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="E41" s="55"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K31" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K41" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2843,90 +2890,90 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>48</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>49</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>50</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>57</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>58</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>59</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>60</v>
-      </c>
-      <c r="I2" t="s">
-        <v>61</v>
       </c>
       <c r="J2">
         <v>4.0901</v>
       </c>
       <c r="M2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O2">
         <v>110</v>
       </c>
       <c r="P2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="str">
         <f>VLOOKUP(C2,型号!A:C,3,0)</f>
@@ -2943,37 +2990,37 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
       <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>65</v>
-      </c>
       <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" t="s">
         <v>59</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>60</v>
-      </c>
-      <c r="I3" t="s">
-        <v>61</v>
       </c>
       <c r="J3">
         <v>4.0901</v>
       </c>
       <c r="M3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O3">
         <v>110</v>
       </c>
       <c r="P3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="str">
         <f>VLOOKUP(C3,型号!A:C,3,0)</f>
@@ -2990,37 +3037,37 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
       <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
       </c>
       <c r="J4">
         <v>5.0536</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O4">
         <v>110</v>
       </c>
       <c r="P4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="str">
         <f>VLOOKUP(C4,型号!A:C,3,0)</f>
@@ -3037,37 +3084,37 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
       <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
       <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>60</v>
-      </c>
-      <c r="I5" t="s">
-        <v>61</v>
       </c>
       <c r="J5">
         <v>2.2925</v>
       </c>
       <c r="M5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O5">
         <v>110</v>
       </c>
       <c r="P5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="str">
         <f>VLOOKUP(C5,型号!A:C,3,0)</f>
@@ -3084,37 +3131,37 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
       <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
       <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
         <v>59</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>60</v>
-      </c>
-      <c r="I6" t="s">
-        <v>61</v>
       </c>
       <c r="J6">
         <v>3.4712</v>
       </c>
       <c r="M6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O6">
         <v>110</v>
       </c>
       <c r="P6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="str">
         <f>VLOOKUP(C6,型号!A:C,3,0)</f>
@@ -3131,37 +3178,37 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
       <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
       <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" t="s">
         <v>59</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>60</v>
-      </c>
-      <c r="I7" t="s">
-        <v>61</v>
       </c>
       <c r="J7">
         <v>3.7914</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O7">
         <v>110</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="str">
         <f>VLOOKUP(C7,型号!A:C,3,0)</f>
@@ -3178,37 +3225,37 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
       <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>60</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
         <v>61</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>62</v>
       </c>
       <c r="O8">
         <v>110</v>
       </c>
       <c r="P8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q8" t="str">
         <f>VLOOKUP(C8,型号!A:C,3,0)</f>
@@ -3225,37 +3272,37 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
       <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
       <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
         <v>59</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
       </c>
       <c r="J9">
         <v>3.7914</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O9">
         <v>110</v>
       </c>
       <c r="P9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="str">
         <f>VLOOKUP(C9,型号!A:C,3,0)</f>
@@ -3272,37 +3319,37 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
       <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
       <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>60</v>
-      </c>
-      <c r="I10" t="s">
-        <v>61</v>
       </c>
       <c r="J10" s="8">
         <v>8.4438</v>
       </c>
       <c r="M10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O10">
         <v>110</v>
       </c>
       <c r="P10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="str">
         <f>VLOOKUP(C10,型号!A:C,3,0)</f>
@@ -3319,37 +3366,37 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
       <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
         <v>80</v>
       </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
       <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>60</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
         <v>61</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>62</v>
       </c>
       <c r="O11">
         <v>110</v>
       </c>
       <c r="P11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q11" t="str">
         <f>VLOOKUP(C11,型号!A:C,3,0)</f>
@@ -3366,37 +3413,37 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
       <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
         <v>82</v>
       </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
       <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
         <v>59</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>60</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
         <v>61</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>62</v>
       </c>
       <c r="O12">
         <v>110</v>
       </c>
       <c r="P12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q12" t="str">
         <f>VLOOKUP(C12,型号!A:C,3,0)</f>
@@ -3413,37 +3460,37 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
       <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
         <v>84</v>
       </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
       <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" t="s">
         <v>59</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>60</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
         <v>61</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>62</v>
       </c>
       <c r="O13">
         <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" t="str">
         <f>VLOOKUP(C13,型号!A:C,3,0)</f>
@@ -3460,37 +3507,37 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
       <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
       <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
         <v>59</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>60</v>
-      </c>
-      <c r="I14" t="s">
-        <v>61</v>
       </c>
       <c r="J14">
         <v>4.0901</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O14">
         <v>110</v>
       </c>
       <c r="P14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" t="str">
         <f>VLOOKUP(C14,型号!A:C,3,0)</f>
@@ -3507,37 +3554,37 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
       <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
       <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s">
         <v>59</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>60</v>
-      </c>
-      <c r="I15" t="s">
-        <v>61</v>
       </c>
       <c r="J15" s="8">
         <v>8.4438</v>
       </c>
       <c r="M15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O15">
         <v>110</v>
       </c>
       <c r="P15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q15" t="str">
         <f>VLOOKUP(C15,型号!A:C,3,0)</f>
@@ -3554,37 +3601,37 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
       <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
       <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" t="s">
         <v>59</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>60</v>
-      </c>
-      <c r="I16" t="s">
-        <v>61</v>
       </c>
       <c r="J16">
         <v>5.2113</v>
       </c>
       <c r="M16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O16">
         <v>110</v>
       </c>
       <c r="P16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q16" t="str">
         <f>VLOOKUP(C16,型号!A:C,3,0)</f>
@@ -3601,37 +3648,37 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
       <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
         <v>92</v>
       </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
       <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>60</v>
-      </c>
-      <c r="I17" t="s">
-        <v>61</v>
       </c>
       <c r="J17">
         <v>3.7914</v>
       </c>
       <c r="M17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O17">
         <v>110</v>
       </c>
       <c r="P17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q17" t="str">
         <f>VLOOKUP(C17,型号!A:C,3,0)</f>
@@ -3648,37 +3695,37 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
       <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
       <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
         <v>59</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>60</v>
-      </c>
-      <c r="I18" t="s">
-        <v>61</v>
       </c>
       <c r="J18">
         <v>3.4712</v>
       </c>
       <c r="M18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O18">
         <v>110</v>
       </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q18" t="str">
         <f>VLOOKUP(C18,型号!A:C,3,0)</f>
@@ -3695,37 +3742,37 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
         <v>96</v>
       </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" t="s">
         <v>59</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>60</v>
-      </c>
-      <c r="I19" t="s">
-        <v>61</v>
       </c>
       <c r="J19">
         <v>3.4712</v>
       </c>
       <c r="M19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O19">
         <v>110</v>
       </c>
       <c r="P19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q19" t="str">
         <f>VLOOKUP(C19,型号!A:C,3,0)</f>
@@ -3742,37 +3789,37 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
       <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
         <v>59</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>60</v>
-      </c>
-      <c r="I20" t="s">
-        <v>61</v>
       </c>
       <c r="J20">
         <v>4.0901</v>
       </c>
       <c r="M20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O20">
         <v>110</v>
       </c>
       <c r="P20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q20" t="str">
         <f>VLOOKUP(C20,型号!A:C,3,0)</f>
@@ -3789,37 +3836,37 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
       <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
       <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" t="s">
         <v>59</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>60</v>
-      </c>
-      <c r="I21" t="s">
-        <v>61</v>
       </c>
       <c r="J21">
         <v>2.9837</v>
       </c>
       <c r="M21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O21">
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q21" t="str">
         <f>VLOOKUP(C21,型号!A:C,3,0)</f>
@@ -3836,37 +3883,37 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
         <v>55</v>
       </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
       <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
       <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
         <v>59</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>60</v>
-      </c>
-      <c r="I22" t="s">
-        <v>61</v>
       </c>
       <c r="J22" s="8">
         <v>8.4438</v>
       </c>
       <c r="M22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O22">
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q22" t="str">
         <f>VLOOKUP(C22,型号!A:C,3,0)</f>
@@ -3883,37 +3930,37 @@
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
       <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
-        <v>105</v>
-      </c>
       <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" t="s">
         <v>59</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>60</v>
-      </c>
-      <c r="I23" t="s">
-        <v>61</v>
       </c>
       <c r="J23" s="8">
         <v>8.4438</v>
       </c>
       <c r="M23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O23">
         <v>110</v>
       </c>
       <c r="P23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q23" t="str">
         <f>VLOOKUP(C23,型号!A:C,3,0)</f>
@@ -3930,37 +3977,37 @@
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
       </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
       <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
         <v>106</v>
       </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
       <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" t="s">
         <v>59</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>61</v>
       </c>
       <c r="J24">
         <v>3.4712</v>
       </c>
       <c r="M24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O24">
         <v>110</v>
       </c>
       <c r="P24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q24" t="str">
         <f>VLOOKUP(C24,型号!A:C,3,0)</f>
@@ -3977,37 +4024,37 @@
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
       <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
         <v>108</v>
       </c>
-      <c r="D25" t="s">
-        <v>109</v>
-      </c>
       <c r="E25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
         <v>59</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>61</v>
       </c>
       <c r="J25">
         <v>5.0536</v>
       </c>
       <c r="M25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O25">
         <v>110</v>
       </c>
       <c r="P25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q25" t="str">
         <f>VLOOKUP(C25,型号!A:C,3,0)</f>
@@ -4024,37 +4071,37 @@
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
       <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
         <v>110</v>
       </c>
-      <c r="D26" t="s">
-        <v>111</v>
-      </c>
       <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" t="s">
         <v>59</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>60</v>
-      </c>
-      <c r="I26" t="s">
-        <v>61</v>
       </c>
       <c r="J26" s="8">
         <v>8.4438</v>
       </c>
       <c r="M26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O26">
         <v>110</v>
       </c>
       <c r="P26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q26" t="str">
         <f>VLOOKUP(C26,型号!A:C,3,0)</f>
@@ -4071,37 +4118,37 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
         <v>55</v>
       </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
       <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
         <v>112</v>
       </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
       <c r="E27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" t="s">
         <v>59</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>60</v>
-      </c>
-      <c r="I27" t="s">
-        <v>61</v>
       </c>
       <c r="J27" s="8">
         <v>8.4438</v>
       </c>
       <c r="M27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O27">
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q27" t="str">
         <f>VLOOKUP(C27,型号!A:C,3,0)</f>
@@ -4118,37 +4165,37 @@
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
       <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
         <v>114</v>
       </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
       <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" t="s">
         <v>59</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>60</v>
-      </c>
-      <c r="I28" t="s">
-        <v>61</v>
       </c>
       <c r="J28">
         <v>1490.092</v>
       </c>
       <c r="M28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O28">
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="str">
         <f>VLOOKUP(C28,型号!A:C,3,0)</f>
@@ -4165,37 +4212,37 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
       <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
       <c r="E29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" t="s">
         <v>59</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>60</v>
-      </c>
-      <c r="I29" t="s">
-        <v>61</v>
       </c>
       <c r="J29">
         <v>11.2214</v>
       </c>
       <c r="M29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O29">
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q29" t="str">
         <f>VLOOKUP(C29,型号!A:C,3,0)</f>
@@ -4212,37 +4259,37 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
       <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
         <v>118</v>
       </c>
-      <c r="D30" t="s">
-        <v>119</v>
-      </c>
       <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" t="s">
         <v>59</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>60</v>
-      </c>
-      <c r="I30" t="s">
-        <v>61</v>
       </c>
       <c r="J30">
         <v>250.5673</v>
       </c>
       <c r="M30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O30">
         <v>110</v>
       </c>
       <c r="P30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q30" t="str">
         <f>VLOOKUP(C30,型号!A:C,3,0)</f>
@@ -4259,37 +4306,37 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
       <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
-        <v>121</v>
-      </c>
       <c r="E31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" t="s">
         <v>59</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>60</v>
-      </c>
-      <c r="I31" t="s">
-        <v>61</v>
       </c>
       <c r="J31">
         <v>12.745</v>
       </c>
       <c r="M31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O31">
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q31" t="str">
         <f>VLOOKUP(C31,型号!A:C,3,0)</f>
@@ -4306,37 +4353,37 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
         <v>55</v>
       </c>
-      <c r="B32" t="s">
-        <v>56</v>
-      </c>
       <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
         <v>122</v>
       </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
       <c r="E32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" t="s">
         <v>59</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>61</v>
       </c>
       <c r="J32" s="8">
         <v>8.4438</v>
       </c>
       <c r="M32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O32">
         <v>110</v>
       </c>
       <c r="P32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q32" t="str">
         <f>VLOOKUP(C32,型号!A:C,3,0)</f>
@@ -4353,37 +4400,37 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
         <v>55</v>
       </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
       <c r="C33" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" t="s">
         <v>124</v>
       </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
       <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
         <v>60</v>
-      </c>
-      <c r="I33" t="s">
-        <v>61</v>
       </c>
       <c r="J33">
         <v>31.8244</v>
       </c>
       <c r="M33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O33">
         <v>110</v>
       </c>
       <c r="P33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q33" t="str">
         <f>VLOOKUP(C33,型号!A:C,3,0)</f>
@@ -4400,37 +4447,37 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s">
-        <v>56</v>
-      </c>
       <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
-        <v>127</v>
-      </c>
       <c r="E34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" t="s">
         <v>59</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>60</v>
-      </c>
-      <c r="I34" t="s">
-        <v>61</v>
       </c>
       <c r="J34">
         <v>31.8244</v>
       </c>
       <c r="M34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O34">
         <v>110</v>
       </c>
       <c r="P34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q34" t="str">
         <f>VLOOKUP(C34,型号!A:C,3,0)</f>
@@ -4447,37 +4494,37 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
       <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" t="s">
         <v>128</v>
       </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
       <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" t="s">
         <v>59</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>60</v>
-      </c>
-      <c r="I35" t="s">
-        <v>61</v>
       </c>
       <c r="J35">
         <v>7.8846</v>
       </c>
       <c r="M35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O35">
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q35" t="str">
         <f>VLOOKUP(C35,型号!A:C,3,0)</f>
@@ -4494,37 +4541,37 @@
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
         <v>55</v>
       </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
       <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="s">
         <v>130</v>
       </c>
-      <c r="D36" t="s">
-        <v>131</v>
-      </c>
       <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" t="s">
         <v>59</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
         <v>60</v>
-      </c>
-      <c r="I36" t="s">
-        <v>61</v>
       </c>
       <c r="J36" s="8">
         <v>8.4438</v>
       </c>
       <c r="M36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O36">
         <v>110</v>
       </c>
       <c r="P36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q36" t="str">
         <f>VLOOKUP(C36,型号!A:C,3,0)</f>
@@ -4541,37 +4588,37 @@
     </row>
     <row r="37" s="5" customFormat="1" spans="1:19">
       <c r="A37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="C37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="E37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="J37" s="8">
         <v>8.4438</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O37" s="5">
         <v>110</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q37" s="5" t="str">
         <f>VLOOKUP(C37,型号!A:C,3,0)</f>
@@ -4603,7 +4650,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4628,90 +4675,90 @@
   <sheetData>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>44</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>46</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>47</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>48</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>49</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>50</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>51</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>52</v>
       </c>
-      <c r="P2" t="s">
-        <v>53</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="1:19">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>57</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>59</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>60</v>
-      </c>
-      <c r="I3" t="s">
-        <v>61</v>
       </c>
       <c r="J3">
         <v>4.3874</v>
       </c>
       <c r="M3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O3">
         <v>220</v>
       </c>
       <c r="P3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
         <v>10</v>
@@ -4726,37 +4773,37 @@
     </row>
     <row r="4" hidden="1" spans="1:19">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
       <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
       <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
       </c>
       <c r="J4">
         <v>4.3874</v>
       </c>
       <c r="M4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O4">
         <v>220</v>
       </c>
       <c r="P4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="s">
         <v>10</v>
@@ -4771,37 +4818,37 @@
     </row>
     <row r="5" hidden="1" spans="1:19">
       <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
         <v>66</v>
       </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
       <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>60</v>
-      </c>
-      <c r="I5" t="s">
-        <v>61</v>
       </c>
       <c r="J5">
         <v>5.4206</v>
       </c>
       <c r="M5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O5">
         <v>220</v>
       </c>
       <c r="P5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
         <v>11</v>
@@ -4816,37 +4863,37 @@
     </row>
     <row r="6" hidden="1" spans="1:19">
       <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
       <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
       <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
         <v>59</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>60</v>
-      </c>
-      <c r="I6" t="s">
-        <v>61</v>
       </c>
       <c r="J6">
         <v>2.2925</v>
       </c>
       <c r="M6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O6">
         <v>220</v>
       </c>
       <c r="P6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="s">
         <v>25</v>
@@ -4861,37 +4908,37 @@
     </row>
     <row r="7" hidden="1" spans="1:19">
       <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
       <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
       <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" t="s">
         <v>59</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>60</v>
-      </c>
-      <c r="I7" t="s">
-        <v>61</v>
       </c>
       <c r="J7">
         <v>3.4623</v>
       </c>
       <c r="M7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O7">
         <v>220</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
         <v>16</v>
@@ -4906,37 +4953,37 @@
     </row>
     <row r="8" hidden="1" spans="1:19">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
       <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
       <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
         <v>59</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>60</v>
-      </c>
-      <c r="I8" t="s">
-        <v>61</v>
       </c>
       <c r="J8">
         <v>4.0649</v>
       </c>
       <c r="M8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O8">
         <v>220</v>
       </c>
       <c r="P8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q8" t="s">
         <v>15</v>
@@ -4951,37 +4998,37 @@
     </row>
     <row r="9" hidden="1" spans="1:19">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
       <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
       <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
         <v>59</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>60</v>
       </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O9">
         <v>220</v>
       </c>
       <c r="P9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="s">
         <v>26</v>
@@ -4996,37 +5043,37 @@
     </row>
     <row r="10" hidden="1" spans="1:19">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
       <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
         <v>76</v>
       </c>
-      <c r="D10" t="s">
-        <v>77</v>
-      </c>
       <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>60</v>
-      </c>
-      <c r="I10" t="s">
-        <v>61</v>
       </c>
       <c r="J10">
         <v>4.0649</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O10">
         <v>220</v>
       </c>
       <c r="P10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="s">
         <v>15</v>
@@ -5041,37 +5088,37 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
       <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
         <v>78</v>
       </c>
-      <c r="D11" t="s">
-        <v>79</v>
-      </c>
       <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>61</v>
       </c>
       <c r="J11">
         <v>8.5529</v>
       </c>
       <c r="M11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O11">
         <v>220</v>
       </c>
       <c r="P11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q11" t="s">
         <v>26</v>
@@ -5086,40 +5133,40 @@
     </row>
     <row r="12" hidden="1" spans="1:19">
       <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
       <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
         <v>80</v>
       </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
       <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
         <v>59</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>60</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
       </c>
       <c r="J12">
         <v>5033.56</v>
       </c>
       <c r="M12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O12">
         <v>220</v>
       </c>
       <c r="P12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -5131,40 +5178,40 @@
     </row>
     <row r="13" hidden="1" spans="1:19">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
       <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
         <v>82</v>
       </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
       <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" t="s">
         <v>59</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>60</v>
-      </c>
-      <c r="I13" t="s">
-        <v>61</v>
       </c>
       <c r="J13">
         <v>5033.56</v>
       </c>
       <c r="M13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O13">
         <v>220</v>
       </c>
       <c r="P13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -5176,40 +5223,40 @@
     </row>
     <row r="14" hidden="1" spans="1:19">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
       <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
         <v>84</v>
       </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
       <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
         <v>59</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>60</v>
-      </c>
-      <c r="I14" t="s">
-        <v>61</v>
       </c>
       <c r="J14">
         <v>1500</v>
       </c>
       <c r="M14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O14">
         <v>220</v>
       </c>
       <c r="P14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5221,37 +5268,37 @@
     </row>
     <row r="15" hidden="1" spans="1:19">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
       <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
         <v>86</v>
       </c>
-      <c r="D15" t="s">
-        <v>87</v>
-      </c>
       <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s">
         <v>59</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>60</v>
-      </c>
-      <c r="I15" t="s">
-        <v>61</v>
       </c>
       <c r="J15">
         <v>4.3874</v>
       </c>
       <c r="M15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O15">
         <v>220</v>
       </c>
       <c r="P15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q15" t="s">
         <v>10</v>
@@ -5266,37 +5313,37 @@
     </row>
     <row r="16" hidden="1" spans="1:19">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
       <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
       <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" t="s">
         <v>59</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>60</v>
-      </c>
-      <c r="I16" t="s">
-        <v>61</v>
       </c>
       <c r="J16">
         <v>8.5529</v>
       </c>
       <c r="M16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O16">
         <v>220</v>
       </c>
       <c r="P16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q16" t="s">
         <v>26</v>
@@ -5311,37 +5358,37 @@
     </row>
     <row r="17" hidden="1" spans="1:19">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
       <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
         <v>90</v>
       </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
       <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>60</v>
-      </c>
-      <c r="I17" t="s">
-        <v>61</v>
       </c>
       <c r="J17">
         <v>5.7392</v>
       </c>
       <c r="M17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O17">
         <v>220</v>
       </c>
       <c r="P17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q17" t="s">
         <v>14</v>
@@ -5356,37 +5403,37 @@
     </row>
     <row r="18" hidden="1" spans="1:19">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
       <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
         <v>92</v>
       </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
       <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
         <v>59</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>60</v>
-      </c>
-      <c r="I18" t="s">
-        <v>61</v>
       </c>
       <c r="J18">
         <v>4.0649</v>
       </c>
       <c r="M18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O18">
         <v>220</v>
       </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q18" t="s">
         <v>15</v>
@@ -5401,37 +5448,37 @@
     </row>
     <row r="19" hidden="1" spans="1:19">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
       <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
         <v>94</v>
       </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" t="s">
         <v>59</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>60</v>
-      </c>
-      <c r="I19" t="s">
-        <v>61</v>
       </c>
       <c r="J19">
         <v>3.4623</v>
       </c>
       <c r="M19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O19">
         <v>220</v>
       </c>
       <c r="P19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q19" t="s">
         <v>16</v>
@@ -5446,37 +5493,37 @@
     </row>
     <row r="20" hidden="1" spans="1:19">
       <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
       <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>96</v>
       </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
         <v>59</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>60</v>
-      </c>
-      <c r="I20" t="s">
-        <v>61</v>
       </c>
       <c r="J20">
         <v>3.4623</v>
       </c>
       <c r="M20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O20">
         <v>220</v>
       </c>
       <c r="P20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q20" t="s">
         <v>16</v>
@@ -5491,37 +5538,37 @@
     </row>
     <row r="21" hidden="1" spans="1:19">
       <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
       <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
       <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" t="s">
         <v>59</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>60</v>
-      </c>
-      <c r="I21" t="s">
-        <v>61</v>
       </c>
       <c r="J21">
         <v>4.3874</v>
       </c>
       <c r="M21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O21">
         <v>220</v>
       </c>
       <c r="P21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q21" t="s">
         <v>10</v>
@@ -5536,40 +5583,40 @@
     </row>
     <row r="22" hidden="1" spans="1:19">
       <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
         <v>55</v>
       </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
       <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
       <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
         <v>59</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>60</v>
-      </c>
-      <c r="I22" t="s">
-        <v>61</v>
       </c>
       <c r="J22">
         <v>2.9793</v>
       </c>
       <c r="M22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O22">
         <v>220</v>
       </c>
       <c r="P22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R22">
         <v>2.9899</v>
@@ -5581,37 +5628,37 @@
     </row>
     <row r="23" hidden="1" spans="1:19">
       <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
       <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
         <v>102</v>
       </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
       <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" t="s">
         <v>59</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>60</v>
-      </c>
-      <c r="I23" t="s">
-        <v>61</v>
       </c>
       <c r="J23">
         <v>8.5529</v>
       </c>
       <c r="M23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O23">
         <v>220</v>
       </c>
       <c r="P23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q23" t="s">
         <v>26</v>
@@ -5626,37 +5673,37 @@
     </row>
     <row r="24" hidden="1" spans="1:19">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
       </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
       <c r="C24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
         <v>104</v>
       </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
       <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" t="s">
         <v>59</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>61</v>
       </c>
       <c r="J24">
         <v>8.5529</v>
       </c>
       <c r="M24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O24">
         <v>220</v>
       </c>
       <c r="P24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q24" t="s">
         <v>26</v>
@@ -5671,37 +5718,37 @@
     </row>
     <row r="25" hidden="1" spans="1:19">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
       <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
         <v>106</v>
       </c>
-      <c r="D25" t="s">
-        <v>107</v>
-      </c>
       <c r="E25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
         <v>59</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>61</v>
       </c>
       <c r="J25">
         <v>3.4623</v>
       </c>
       <c r="M25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O25">
         <v>220</v>
       </c>
       <c r="P25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q25" t="s">
         <v>16</v>
@@ -5716,37 +5763,37 @@
     </row>
     <row r="26" hidden="1" spans="1:19">
       <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
       <c r="C26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
         <v>108</v>
       </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
       <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" t="s">
         <v>59</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>60</v>
-      </c>
-      <c r="I26" t="s">
-        <v>61</v>
       </c>
       <c r="J26">
         <v>5.4206</v>
       </c>
       <c r="M26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O26">
         <v>220</v>
       </c>
       <c r="P26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q26" t="s">
         <v>11</v>
@@ -5761,37 +5808,37 @@
     </row>
     <row r="27" hidden="1" spans="1:19">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
         <v>55</v>
       </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
       <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
         <v>110</v>
       </c>
-      <c r="D27" t="s">
-        <v>111</v>
-      </c>
       <c r="E27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" t="s">
         <v>59</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>60</v>
-      </c>
-      <c r="I27" t="s">
-        <v>61</v>
       </c>
       <c r="J27">
         <v>8.5529</v>
       </c>
       <c r="M27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O27">
         <v>220</v>
       </c>
       <c r="P27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q27" t="s">
         <v>26</v>
@@ -5806,37 +5853,37 @@
     </row>
     <row r="28" hidden="1" spans="1:19">
       <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
       <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
         <v>112</v>
       </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
       <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" t="s">
         <v>59</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>60</v>
-      </c>
-      <c r="I28" t="s">
-        <v>61</v>
       </c>
       <c r="J28">
         <v>8.5529</v>
       </c>
       <c r="M28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O28">
         <v>220</v>
       </c>
       <c r="P28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="s">
         <v>26</v>
@@ -5851,40 +5898,40 @@
     </row>
     <row r="29" hidden="1" spans="1:19">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
       <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
         <v>114</v>
       </c>
-      <c r="D29" t="s">
-        <v>115</v>
-      </c>
       <c r="E29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" t="s">
         <v>59</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>60</v>
-      </c>
-      <c r="I29" t="s">
-        <v>61</v>
       </c>
       <c r="J29">
         <v>1080.1792</v>
       </c>
       <c r="M29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O29">
         <v>220</v>
       </c>
       <c r="P29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R29">
         <v>69.0336</v>
@@ -5896,40 +5943,40 @@
     </row>
     <row r="30" hidden="1" spans="1:19">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
       <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
         <v>116</v>
       </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
       <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" t="s">
         <v>59</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>60</v>
-      </c>
-      <c r="I30" t="s">
-        <v>61</v>
       </c>
       <c r="J30">
         <v>11.7402</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O30">
         <v>220</v>
       </c>
       <c r="P30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R30">
         <v>11.2362</v>
@@ -5941,37 +5988,37 @@
     </row>
     <row r="31" hidden="1" spans="1:19">
       <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
       <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
         <v>118</v>
       </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
       <c r="E31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" t="s">
         <v>59</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>60</v>
-      </c>
-      <c r="I31" t="s">
-        <v>61</v>
       </c>
       <c r="J31">
         <v>250.5673</v>
       </c>
       <c r="M31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O31">
         <v>220</v>
       </c>
       <c r="P31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q31" t="s">
         <v>22</v>
@@ -5986,40 +6033,40 @@
     </row>
     <row r="32" hidden="1" spans="1:19">
       <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
         <v>55</v>
       </c>
-      <c r="B32" t="s">
-        <v>56</v>
-      </c>
       <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
         <v>120</v>
       </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
       <c r="E32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" t="s">
         <v>59</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>61</v>
       </c>
       <c r="J32">
         <v>11.2528</v>
       </c>
       <c r="M32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O32">
         <v>220</v>
       </c>
       <c r="P32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R32">
         <v>11.213</v>
@@ -6031,37 +6078,37 @@
     </row>
     <row r="33" hidden="1" spans="1:19">
       <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
         <v>55</v>
       </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
       <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
       <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
         <v>60</v>
-      </c>
-      <c r="I33" t="s">
-        <v>61</v>
       </c>
       <c r="J33">
         <v>8.5529</v>
       </c>
       <c r="M33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O33">
         <v>220</v>
       </c>
       <c r="P33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q33" t="s">
         <v>26</v>
@@ -6076,40 +6123,40 @@
     </row>
     <row r="34" hidden="1" spans="1:19">
       <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s">
-        <v>56</v>
-      </c>
       <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" t="s">
         <v>124</v>
       </c>
-      <c r="D34" t="s">
-        <v>125</v>
-      </c>
       <c r="E34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" t="s">
         <v>59</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>60</v>
-      </c>
-      <c r="I34" t="s">
-        <v>61</v>
       </c>
       <c r="J34">
         <v>31.5585</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O34">
         <v>220</v>
       </c>
       <c r="P34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R34">
         <v>31.8244</v>
@@ -6121,37 +6168,37 @@
     </row>
     <row r="35" hidden="1" spans="1:19">
       <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
       <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
         <v>126</v>
       </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
       <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" t="s">
         <v>59</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>60</v>
-      </c>
-      <c r="I35" t="s">
-        <v>61</v>
       </c>
       <c r="J35">
         <v>31.5585</v>
       </c>
       <c r="M35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O35">
         <v>220</v>
       </c>
       <c r="P35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q35" t="e">
         <v>#N/A</v>
@@ -6191,169 +6238,169 @@
   <sheetData>
     <row r="2" spans="1:56">
       <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>139</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>140</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>141</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>142</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>143</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>144</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
         <v>145</v>
       </c>
-      <c r="J2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>146</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>147</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>148</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>149</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>150</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>151</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>152</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>153</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>154</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>155</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>156</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>157</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>158</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>159</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>160</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>161</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>162</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>163</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>164</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>165</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>166</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>167</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>168</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>169</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>170</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>171</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM2" t="s">
         <v>172</v>
       </c>
-      <c r="AL2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>173</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>174</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>175</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>176</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>177</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>178</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>179</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW2" t="s">
         <v>180</v>
       </c>
-      <c r="AU2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>181</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>182</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>183</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>184</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>185</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>186</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>187</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:56">
@@ -6364,10 +6411,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="1">
         <v>8.5278</v>
@@ -6376,13 +6423,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K3" s="1" t="e">
         <f>VLOOKUP(D3,#REF!,15,0)</f>
@@ -6400,22 +6447,22 @@
         <v>#REF!</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="BC3" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="BD3" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:56">
@@ -6426,10 +6473,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1">
         <v>8.5278</v>
@@ -6438,13 +6485,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K4" s="1" t="e">
         <f>VLOOKUP(D4,#REF!,15,0)</f>
@@ -6462,22 +6509,22 @@
         <v>#REF!</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="BC4" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="BD4" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD4" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:56">
@@ -6488,10 +6535,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="1">
         <v>5.4151</v>
@@ -6500,13 +6547,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K5" s="1" t="e">
         <f>VLOOKUP(D5,#REF!,15,0)</f>
@@ -6524,22 +6571,22 @@
         <v>#REF!</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="BC5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="BD5" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC5" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:56">
@@ -6550,10 +6597,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1">
         <v>4.0649</v>
@@ -6562,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K6" s="1" t="e">
         <f>VLOOKUP(D6,#REF!,15,0)</f>
@@ -6586,22 +6633,22 @@
         <v>#REF!</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="BC6" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="BD6" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC6" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="1:56">
@@ -6612,10 +6659,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7">
         <v>4.382</v>
@@ -6624,13 +6671,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" t="s">
         <v>190</v>
-      </c>
-      <c r="I7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" t="s">
-        <v>191</v>
       </c>
       <c r="K7" t="e">
         <f>VLOOKUP(D7,#REF!,15,0)</f>
@@ -6648,22 +6695,22 @@
         <v>#REF!</v>
       </c>
       <c r="O7" t="s">
+        <v>191</v>
+      </c>
+      <c r="P7" t="s">
+        <v>191</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="s">
         <v>192</v>
       </c>
-      <c r="P7" t="s">
+      <c r="BC7" t="s">
         <v>192</v>
       </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="s">
+      <c r="BD7" t="s">
         <v>193</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:56">
@@ -6674,10 +6721,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="1">
         <v>8.5278</v>
@@ -6686,13 +6733,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K8" s="1" t="e">
         <f>VLOOKUP(D8,#REF!,15,0)</f>
@@ -6710,22 +6757,22 @@
         <v>#REF!</v>
       </c>
       <c r="O8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="BC8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1" t="s">
+      <c r="BD8" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC8" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD8" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:56">
@@ -6736,10 +6783,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" s="1">
         <v>8.5278</v>
@@ -6748,13 +6795,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K9" s="1" t="e">
         <f>VLOOKUP(D9,#REF!,15,0)</f>
@@ -6772,22 +6819,22 @@
         <v>#REF!</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="BC9" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1" t="s">
+      <c r="BD9" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC9" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD9" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:56">
@@ -6798,10 +6845,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F10" s="1">
         <v>8.5278</v>
@@ -6810,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K10" s="1" t="e">
         <f>VLOOKUP(D10,#REF!,15,0)</f>
@@ -6834,22 +6881,22 @@
         <v>#REF!</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="BC10" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="1" t="s">
+      <c r="BD10" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC10" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD10" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:56">
@@ -6860,10 +6907,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="1">
         <v>5.4151</v>
@@ -6872,13 +6919,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K11" s="1" t="e">
         <f>VLOOKUP(D11,#REF!,15,0)</f>
@@ -6896,22 +6943,22 @@
         <v>#REF!</v>
       </c>
       <c r="O11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="BC11" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1" t="s">
+      <c r="BD11" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD11" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="12" hidden="1" spans="1:56">
@@ -6922,10 +6969,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F12">
         <v>5.4151</v>
@@ -6934,13 +6981,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K12" t="e">
         <f>VLOOKUP(D12,#REF!,15,0)</f>
@@ -6958,22 +7005,22 @@
         <v>#REF!</v>
       </c>
       <c r="O12" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" t="s">
+        <v>191</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="s">
         <v>192</v>
       </c>
-      <c r="P12" t="s">
+      <c r="BC12" t="s">
         <v>192</v>
       </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="s">
+      <c r="BD12" t="s">
         <v>193</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="1:56">
@@ -6984,10 +7031,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13">
         <v>4.382</v>
@@ -6996,13 +7043,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" t="s">
         <v>190</v>
-      </c>
-      <c r="I13" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" t="s">
-        <v>191</v>
       </c>
       <c r="K13" t="e">
         <f>VLOOKUP(D13,#REF!,15,0)</f>
@@ -7020,22 +7067,22 @@
         <v>#REF!</v>
       </c>
       <c r="O13" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" t="s">
+        <v>191</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="s">
         <v>192</v>
       </c>
-      <c r="P13" t="s">
+      <c r="BC13" t="s">
         <v>192</v>
       </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="s">
+      <c r="BD13" t="s">
         <v>193</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:56">
@@ -7046,10 +7093,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>4.382</v>
@@ -7058,13 +7105,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" t="s">
         <v>190</v>
-      </c>
-      <c r="I14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" t="s">
-        <v>191</v>
       </c>
       <c r="K14" t="e">
         <f>VLOOKUP(D14,#REF!,15,0)</f>
@@ -7082,22 +7129,22 @@
         <v>#REF!</v>
       </c>
       <c r="O14" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" t="s">
+        <v>191</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="s">
         <v>192</v>
       </c>
-      <c r="P14" t="s">
+      <c r="BC14" t="s">
         <v>192</v>
       </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="s">
+      <c r="BD14" t="s">
         <v>193</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:56">
@@ -7108,10 +7155,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1">
         <v>5.4151</v>
@@ -7120,13 +7167,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="K15" s="1" t="e">
         <f>VLOOKUP(D15,#REF!,15,0)</f>
@@ -7144,22 +7191,22 @@
         <v>#REF!</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="BC15" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1" t="s">
+      <c r="BD15" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC15" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD15" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="1:56">
@@ -7170,10 +7217,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16">
         <v>5.4151</v>
@@ -7182,13 +7229,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K16" t="e">
         <f>VLOOKUP(D16,#REF!,15,0)</f>
@@ -7206,22 +7253,22 @@
         <v>#REF!</v>
       </c>
       <c r="O16" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" t="s">
+        <v>191</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
         <v>192</v>
       </c>
-      <c r="P16" t="s">
+      <c r="BC16" t="s">
         <v>192</v>
       </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="s">
+      <c r="BD16" t="s">
         <v>193</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD16" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:56">
@@ -7232,10 +7279,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="1">
         <v>4.0649</v>
@@ -7244,13 +7291,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K17" s="1" t="e">
         <f>VLOOKUP(D17,#REF!,15,0)</f>
@@ -7268,22 +7315,22 @@
         <v>#REF!</v>
       </c>
       <c r="O17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="BC17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="1" t="s">
+      <c r="BD17" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC17" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD17" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="18" hidden="1" spans="1:56">
@@ -7294,10 +7341,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18">
         <v>4.382</v>
@@ -7306,13 +7353,13 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" t="s">
         <v>190</v>
-      </c>
-      <c r="I18" t="s">
-        <v>65</v>
-      </c>
-      <c r="J18" t="s">
-        <v>191</v>
       </c>
       <c r="K18" t="e">
         <f>VLOOKUP(D18,#REF!,15,0)</f>
@@ -7330,22 +7377,22 @@
         <v>#REF!</v>
       </c>
       <c r="O18" t="s">
+        <v>191</v>
+      </c>
+      <c r="P18" t="s">
+        <v>191</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="s">
         <v>192</v>
       </c>
-      <c r="P18" t="s">
+      <c r="BC18" t="s">
         <v>192</v>
       </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="s">
+      <c r="BD18" t="s">
         <v>193</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD18" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:56">
@@ -7356,10 +7403,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="1">
         <v>4.0649</v>
@@ -7368,13 +7415,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K19" s="1" t="e">
         <f>VLOOKUP(D19,#REF!,15,0)</f>
@@ -7392,22 +7439,22 @@
         <v>#REF!</v>
       </c>
       <c r="O19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="BC19" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="X19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="1" t="s">
+      <c r="BD19" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="BC19" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD19" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="1:56">
@@ -7418,10 +7465,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20">
         <v>4.382</v>
@@ -7430,13 +7477,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" t="s">
         <v>190</v>
-      </c>
-      <c r="I20" t="s">
-        <v>65</v>
-      </c>
-      <c r="J20" t="s">
-        <v>191</v>
       </c>
       <c r="K20" t="e">
         <f>VLOOKUP(D20,#REF!,15,0)</f>
@@ -7454,22 +7501,22 @@
         <v>#REF!</v>
       </c>
       <c r="O20" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" t="s">
+        <v>191</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
         <v>192</v>
       </c>
-      <c r="P20" t="s">
+      <c r="BC20" t="s">
         <v>192</v>
       </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="s">
+      <c r="BD20" t="s">
         <v>193</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD20" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -7501,21 +7548,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
-        <v>41</v>
-      </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -7523,10 +7570,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
         <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -7534,10 +7581,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
         <v>66</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -7545,10 +7592,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
         <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -7556,10 +7603,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -7567,10 +7614,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
         <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -7578,21 +7625,21 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" t="s">
         <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -7600,10 +7647,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
         <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -7611,43 +7658,43 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
       </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
         <v>82</v>
       </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
         <v>84</v>
       </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
         <v>86</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -7655,10 +7702,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
         <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -7666,10 +7713,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
         <v>90</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -7677,10 +7724,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
         <v>92</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -7688,10 +7735,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
         <v>94</v>
-      </c>
-      <c r="B18" t="s">
-        <v>95</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -7699,10 +7746,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
         <v>96</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -7710,10 +7757,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
         <v>98</v>
-      </c>
-      <c r="B20" t="s">
-        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -7721,21 +7768,21 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
         <v>100</v>
       </c>
-      <c r="B21" t="s">
-        <v>101</v>
-      </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
         <v>102</v>
-      </c>
-      <c r="B22" t="s">
-        <v>103</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
@@ -7743,10 +7790,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" t="s">
         <v>104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>105</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -7754,10 +7801,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
         <v>106</v>
-      </c>
-      <c r="B24" t="s">
-        <v>107</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -7765,10 +7812,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
         <v>108</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -7776,10 +7823,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s">
         <v>110</v>
-      </c>
-      <c r="B26" t="s">
-        <v>111</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
@@ -7787,10 +7834,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s">
         <v>112</v>
-      </c>
-      <c r="B27" t="s">
-        <v>113</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
@@ -7798,32 +7845,32 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
         <v>114</v>
       </c>
-      <c r="B28" t="s">
-        <v>115</v>
-      </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
         <v>116</v>
       </c>
-      <c r="B29" t="s">
-        <v>117</v>
-      </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
         <v>118</v>
-      </c>
-      <c r="B30" t="s">
-        <v>119</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -7831,21 +7878,21 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
         <v>120</v>
       </c>
-      <c r="B31" t="s">
-        <v>121</v>
-      </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
         <v>122</v>
-      </c>
-      <c r="B32" t="s">
-        <v>123</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -7853,43 +7900,43 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
         <v>124</v>
       </c>
-      <c r="B33" t="s">
-        <v>125</v>
-      </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" t="s">
         <v>126</v>
       </c>
-      <c r="B34" t="s">
-        <v>127</v>
-      </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
         <v>128</v>
       </c>
-      <c r="B35" t="s">
-        <v>129</v>
-      </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
         <v>130</v>
-      </c>
-      <c r="B36" t="s">
-        <v>131</v>
       </c>
       <c r="C36" t="s">
         <v>26</v>
@@ -7897,10 +7944,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
         <v>132</v>
-      </c>
-      <c r="B37" t="s">
-        <v>133</v>
       </c>
       <c r="C37" t="s">
         <v>26</v>
